--- a/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
+++ b/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/users/nathaniyer/library/containers/com.microsoft.excel/data/state-eps-data-repository/template_state/land/fofobe/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\land\FoFObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863AE3C9-68C8-014B-86B6-4C7C34B9D87F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D0EA2B-02FF-453F-9596-BFD3D1EA0E4A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="460" windowWidth="19140" windowHeight="9280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>FoFObE Fraction of Forests Owned by Entity</t>
   </si>
@@ -101,52 +101,13 @@
     <t>foreign entities</t>
   </si>
   <si>
-    <t>nonenergy industries</t>
-  </si>
-  <si>
     <t>labor and consumers</t>
   </si>
   <si>
-    <t>electricity suppliers</t>
-  </si>
-  <si>
-    <t>coal suppliers</t>
-  </si>
-  <si>
-    <t>natural gas and petroleum suppliers</t>
-  </si>
-  <si>
-    <t>biomass and biofuel suppliers</t>
-  </si>
-  <si>
-    <t>other energy suppliers</t>
-  </si>
-  <si>
-    <t>Though some industry-owned timber land might be used to</t>
-  </si>
-  <si>
-    <t>produce biomass, but not all biomass is wood, and</t>
-  </si>
-  <si>
-    <t>much of the wood biomass is waste (bark, sawdust, chips, scrap,</t>
-  </si>
-  <si>
-    <t>and paper mill residues), which is not the main product</t>
-  </si>
-  <si>
-    <t>of the timber lands.  Accordingly, we assign timber land</t>
-  </si>
-  <si>
-    <t>ownership to "nonenergy industries" rather than assigning</t>
-  </si>
-  <si>
-    <t>a share to "biomass and biofuel suppliers."</t>
-  </si>
-  <si>
-    <t>Biomass</t>
-  </si>
-  <si>
     <t>Fraction of Forest Owned (dimensionless)</t>
+  </si>
+  <si>
+    <t>domestic industries</t>
   </si>
 </sst>
 </file>
@@ -202,7 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -219,7 +180,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -559,18 +519,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8">
-        <v>44307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -578,89 +535,49 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>2001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -675,22 +592,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -698,7 +615,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -706,7 +623,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -714,7 +631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -722,7 +639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -730,7 +647,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -738,7 +655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -746,7 +663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -754,7 +671,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -762,7 +679,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -770,7 +687,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -778,7 +695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
@@ -786,7 +703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -794,7 +711,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -802,7 +719,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -810,7 +727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
@@ -829,19 +746,19 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -850,69 +767,29 @@
         <v>0.42384105960264901</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="5">
         <f>SUM(Data!B11,Data!B16,Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
         <v>0.52814569536423839</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="5">
         <f>(Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
         <v>4.8013245033112585E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10">
         <v>0</v>
       </c>
     </row>
